--- a/project/data/AHD_Asthma_FY2022.xlsx
+++ b/project/data/AHD_Asthma_FY2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexramiller/Library/CloudStorage/Dropbox/Git/ggr274/20261/project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272CE1D9-1870-B241-8B4E-5D04FDF0CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11EAEDD-18A9-3840-9A2F-818A917FA9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="760" windowWidth="29440" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,9 +744,6 @@
     <t>Total Population 2023 (RPDB), All Ages 0+</t>
   </si>
   <si>
-    <t xml:space="preserve"> Age-Standardized rate (/100) of Asthma (2021/22), All Ages 0+</t>
-  </si>
-  <si>
     <t># of people with asthma 2021/22, Age 0-19</t>
   </si>
   <si>
@@ -769,6 +766,9 @@
   </si>
   <si>
     <t>Total Population 2023 (RPDB), Age 65+</t>
+  </si>
+  <si>
+    <t>Age-Standardized rate (/100) of Asthma (2021/22), All Ages 0+</t>
   </si>
 </sst>
 </file>
@@ -1608,6 +1608,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1615,6 +1627,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="22" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1644,29 +1665,8 @@
     <xf numFmtId="1" fontId="22" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -2269,144 +2269,144 @@
       <c r="N2"/>
     </row>
     <row r="3" spans="1:98" s="31" customFormat="1" ht="33" customHeight="1" thickBot="1">
-      <c r="A3" s="154" t="s">
+      <c r="A3" s="138" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="155"/>
-      <c r="C3" s="136" t="s">
+      <c r="B3" s="139"/>
+      <c r="C3" s="140" t="s">
         <v>226</v>
       </c>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="136" t="s">
+      <c r="D3" s="141"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="140" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="137"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="148" t="s">
+      <c r="G3" s="141"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="143" t="s">
+        <v>236</v>
+      </c>
+      <c r="J3" s="144"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="144"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="144"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="144"/>
+      <c r="Q3" s="144"/>
+      <c r="R3" s="144"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="140" t="s">
+        <v>212</v>
+      </c>
+      <c r="U3" s="141"/>
+      <c r="V3" s="141"/>
+      <c r="W3" s="141"/>
+      <c r="X3" s="141"/>
+      <c r="Y3" s="141"/>
+      <c r="Z3" s="141"/>
+      <c r="AA3" s="141"/>
+      <c r="AB3" s="141"/>
+      <c r="AC3" s="141"/>
+      <c r="AD3" s="142"/>
+      <c r="AE3" s="146" t="s">
         <v>228</v>
       </c>
-      <c r="J3" s="149"/>
-      <c r="K3" s="149"/>
-      <c r="L3" s="149"/>
-      <c r="M3" s="149"/>
-      <c r="N3" s="149"/>
-      <c r="O3" s="149"/>
-      <c r="P3" s="149"/>
-      <c r="Q3" s="149"/>
-      <c r="R3" s="149"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="136" t="s">
-        <v>212</v>
-      </c>
-      <c r="U3" s="137"/>
-      <c r="V3" s="137"/>
-      <c r="W3" s="137"/>
-      <c r="X3" s="137"/>
-      <c r="Y3" s="137"/>
-      <c r="Z3" s="137"/>
-      <c r="AA3" s="137"/>
-      <c r="AB3" s="137"/>
-      <c r="AC3" s="137"/>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="139" t="s">
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="148"/>
+      <c r="AH3" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="AF3" s="140"/>
-      <c r="AG3" s="141"/>
-      <c r="AH3" s="142" t="s">
+      <c r="AI3" s="149"/>
+      <c r="AJ3" s="150"/>
+      <c r="AK3" s="151" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL3" s="149"/>
+      <c r="AM3" s="149"/>
+      <c r="AN3" s="149"/>
+      <c r="AO3" s="149"/>
+      <c r="AP3" s="149"/>
+      <c r="AQ3" s="149"/>
+      <c r="AR3" s="149"/>
+      <c r="AS3" s="149"/>
+      <c r="AT3" s="149"/>
+      <c r="AU3" s="150"/>
+      <c r="AV3" s="152" t="s">
         <v>230</v>
       </c>
-      <c r="AI3" s="142"/>
-      <c r="AJ3" s="143"/>
-      <c r="AK3" s="144" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL3" s="142"/>
-      <c r="AM3" s="142"/>
-      <c r="AN3" s="142"/>
-      <c r="AO3" s="142"/>
-      <c r="AP3" s="142"/>
-      <c r="AQ3" s="142"/>
-      <c r="AR3" s="142"/>
-      <c r="AS3" s="142"/>
-      <c r="AT3" s="142"/>
-      <c r="AU3" s="143"/>
-      <c r="AV3" s="145" t="s">
+      <c r="AW3" s="153"/>
+      <c r="AX3" s="154"/>
+      <c r="AY3" s="141" t="s">
         <v>231</v>
       </c>
-      <c r="AW3" s="146"/>
-      <c r="AX3" s="147"/>
-      <c r="AY3" s="137" t="s">
+      <c r="AZ3" s="141"/>
+      <c r="BA3" s="142"/>
+      <c r="BB3" s="140" t="s">
+        <v>214</v>
+      </c>
+      <c r="BC3" s="141"/>
+      <c r="BD3" s="141"/>
+      <c r="BE3" s="141"/>
+      <c r="BF3" s="141"/>
+      <c r="BG3" s="141"/>
+      <c r="BH3" s="141"/>
+      <c r="BI3" s="141"/>
+      <c r="BJ3" s="141"/>
+      <c r="BK3" s="141"/>
+      <c r="BL3" s="142"/>
+      <c r="BM3" s="151" t="s">
         <v>232</v>
       </c>
-      <c r="AZ3" s="137"/>
-      <c r="BA3" s="138"/>
-      <c r="BB3" s="136" t="s">
-        <v>214</v>
-      </c>
-      <c r="BC3" s="137"/>
-      <c r="BD3" s="137"/>
-      <c r="BE3" s="137"/>
-      <c r="BF3" s="137"/>
-      <c r="BG3" s="137"/>
-      <c r="BH3" s="137"/>
-      <c r="BI3" s="137"/>
-      <c r="BJ3" s="137"/>
-      <c r="BK3" s="137"/>
-      <c r="BL3" s="138"/>
-      <c r="BM3" s="144" t="s">
+      <c r="BN3" s="149"/>
+      <c r="BO3" s="150"/>
+      <c r="BP3" s="151" t="s">
         <v>233</v>
       </c>
-      <c r="BN3" s="142"/>
-      <c r="BO3" s="143"/>
-      <c r="BP3" s="144" t="s">
+      <c r="BQ3" s="149"/>
+      <c r="BR3" s="150"/>
+      <c r="BS3" s="151" t="s">
+        <v>215</v>
+      </c>
+      <c r="BT3" s="149"/>
+      <c r="BU3" s="149"/>
+      <c r="BV3" s="149"/>
+      <c r="BW3" s="149"/>
+      <c r="BX3" s="149"/>
+      <c r="BY3" s="149"/>
+      <c r="BZ3" s="149"/>
+      <c r="CA3" s="149"/>
+      <c r="CB3" s="149"/>
+      <c r="CC3" s="150"/>
+      <c r="CD3" s="140" t="s">
         <v>234</v>
       </c>
-      <c r="BQ3" s="142"/>
-      <c r="BR3" s="143"/>
-      <c r="BS3" s="144" t="s">
-        <v>215</v>
-      </c>
-      <c r="BT3" s="142"/>
-      <c r="BU3" s="142"/>
-      <c r="BV3" s="142"/>
-      <c r="BW3" s="142"/>
-      <c r="BX3" s="142"/>
-      <c r="BY3" s="142"/>
-      <c r="BZ3" s="142"/>
-      <c r="CA3" s="142"/>
-      <c r="CB3" s="142"/>
-      <c r="CC3" s="143"/>
-      <c r="CD3" s="136" t="s">
+      <c r="CE3" s="141"/>
+      <c r="CF3" s="142"/>
+      <c r="CG3" s="140" t="s">
         <v>235</v>
       </c>
-      <c r="CE3" s="137"/>
-      <c r="CF3" s="138"/>
-      <c r="CG3" s="136" t="s">
-        <v>236</v>
-      </c>
-      <c r="CH3" s="137"/>
-      <c r="CI3" s="138"/>
-      <c r="CJ3" s="136" t="s">
+      <c r="CH3" s="141"/>
+      <c r="CI3" s="142"/>
+      <c r="CJ3" s="140" t="s">
         <v>216</v>
       </c>
-      <c r="CK3" s="137"/>
-      <c r="CL3" s="137"/>
-      <c r="CM3" s="137"/>
-      <c r="CN3" s="137"/>
-      <c r="CO3" s="137"/>
-      <c r="CP3" s="137"/>
-      <c r="CQ3" s="137"/>
-      <c r="CR3" s="137"/>
-      <c r="CS3" s="137"/>
-      <c r="CT3" s="138"/>
+      <c r="CK3" s="141"/>
+      <c r="CL3" s="141"/>
+      <c r="CM3" s="141"/>
+      <c r="CN3" s="141"/>
+      <c r="CO3" s="141"/>
+      <c r="CP3" s="141"/>
+      <c r="CQ3" s="141"/>
+      <c r="CR3" s="141"/>
+      <c r="CS3" s="141"/>
+      <c r="CT3" s="142"/>
     </row>
     <row r="4" spans="1:98" s="40" customFormat="1" ht="44.5" customHeight="1" thickBot="1">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="153" t="s">
+      <c r="B4" s="137" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="32" t="s">
@@ -49750,11 +49750,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="T3:AD3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:S3"/>
     <mergeCell ref="CJ3:CT3"/>
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AJ3"/>
@@ -49767,6 +49762,11 @@
     <mergeCell ref="BS3:CC3"/>
     <mergeCell ref="CD3:CF3"/>
     <mergeCell ref="CG3:CI3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="T3:AD3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -50080,35 +50080,35 @@
       <c r="A5" s="25">
         <v>1</v>
       </c>
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="151"/>
-      <c r="M5" s="151"/>
+      <c r="C5" s="155"/>
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="23"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
-      <c r="H6" s="151"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="151"/>
-      <c r="L6" s="151"/>
-      <c r="M6" s="151"/>
+      <c r="B6" s="155"/>
+      <c r="C6" s="155"/>
+      <c r="D6" s="155"/>
+      <c r="E6" s="155"/>
+      <c r="F6" s="155"/>
+      <c r="G6" s="155"/>
+      <c r="H6" s="155"/>
+      <c r="I6" s="155"/>
+      <c r="J6" s="155"/>
+      <c r="K6" s="155"/>
+      <c r="L6" s="155"/>
+      <c r="M6" s="155"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="21"/>
